--- a/research/traditional_assets/database/data/panama/panama_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/panama/panama_farming_agriculture.xlsx
@@ -587,8 +587,23 @@
           <t>Farming/Agriculture</t>
         </is>
       </c>
+      <c r="G2">
+        <v>-6.717171717171717</v>
+      </c>
+      <c r="H2">
+        <v>-6.717171717171717</v>
+      </c>
+      <c r="I2">
+        <v>-8.787878787878787</v>
+      </c>
+      <c r="J2">
+        <v>-8.787878787878787</v>
+      </c>
       <c r="K2">
-        <v>-0.845</v>
+        <v>-1.01</v>
+      </c>
+      <c r="L2">
+        <v>-5.101010101010101</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.15</v>
+        <v>0.001</v>
       </c>
       <c r="V2">
-        <v>0.1210526315789474</v>
+        <v>0.0003311258278145695</v>
       </c>
       <c r="W2">
-        <v>0.7971698113207547</v>
+        <v>-0.6273291925465838</v>
       </c>
       <c r="X2">
-        <v>0.06026687225577291</v>
+        <v>0.1226575085251255</v>
       </c>
       <c r="Y2">
-        <v>0.7369029390649818</v>
+        <v>-0.7499867010717093</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>0.4304347826086955</v>
       </c>
       <c r="AA2">
-        <v>-0.3533333333333334</v>
+        <v>-3.782608695652173</v>
       </c>
       <c r="AB2">
-        <v>0.06026687225577291</v>
+        <v>0.1022958695977901</v>
       </c>
       <c r="AC2">
-        <v>-0.4136002055891063</v>
+        <v>-3.884904565249963</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG2">
-        <v>-1.15</v>
+        <v>1.509</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>-0.9096385542168676</v>
       </c>
       <c r="AJ2">
-        <v>-0.1377245508982036</v>
+        <v>0.3331861338043718</v>
       </c>
       <c r="AK2">
-        <v>-2.499999999999999</v>
+        <v>-0.9084888621312465</v>
       </c>
       <c r="AL2">
-        <v>0.209</v>
+        <v>0.172</v>
       </c>
       <c r="AM2">
-        <v>0.209</v>
+        <v>0.172</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>-0.867816091954023</v>
       </c>
       <c r="AO2">
-        <v>-3.043062200956938</v>
+        <v>-10.11627906976744</v>
       </c>
       <c r="AP2">
-        <v>1.975945017182131</v>
+        <v>-0.867241379310345</v>
       </c>
       <c r="AQ2">
-        <v>-3.043062200956938</v>
+        <v>-10.11627906976744</v>
       </c>
     </row>
     <row r="3">
@@ -697,8 +712,23 @@
           <t>Farming/Agriculture</t>
         </is>
       </c>
+      <c r="G3">
+        <v>-6.717171717171717</v>
+      </c>
+      <c r="H3">
+        <v>-6.717171717171717</v>
+      </c>
+      <c r="I3">
+        <v>-8.787878787878787</v>
+      </c>
+      <c r="J3">
+        <v>-8.787878787878787</v>
+      </c>
       <c r="K3">
-        <v>-0.845</v>
+        <v>-1.01</v>
+      </c>
+      <c r="L3">
+        <v>-5.101010101010101</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.15</v>
+        <v>0.001</v>
       </c>
       <c r="V3">
-        <v>0.1210526315789474</v>
+        <v>0.0003311258278145695</v>
       </c>
       <c r="W3">
-        <v>0.7971698113207547</v>
+        <v>-0.6273291925465838</v>
       </c>
       <c r="X3">
-        <v>0.06026687225577291</v>
+        <v>0.1226575085251255</v>
       </c>
       <c r="Y3">
-        <v>0.7369029390649818</v>
+        <v>-0.7499867010717093</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>0.4304347826086955</v>
       </c>
       <c r="AA3">
-        <v>-0.3533333333333334</v>
+        <v>-3.782608695652173</v>
       </c>
       <c r="AB3">
-        <v>0.06026687225577291</v>
+        <v>0.1022958695977901</v>
       </c>
       <c r="AC3">
-        <v>-0.4136002055891063</v>
+        <v>-3.884904565249963</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG3">
-        <v>-1.15</v>
+        <v>1.509</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>-0.9096385542168676</v>
       </c>
       <c r="AJ3">
-        <v>-0.1377245508982036</v>
+        <v>0.3331861338043718</v>
       </c>
       <c r="AK3">
-        <v>-2.499999999999999</v>
+        <v>-0.9084888621312465</v>
       </c>
       <c r="AL3">
-        <v>0.209</v>
+        <v>0.172</v>
       </c>
       <c r="AM3">
-        <v>0.209</v>
+        <v>0.172</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>-0.867816091954023</v>
       </c>
       <c r="AO3">
-        <v>-3.043062200956938</v>
+        <v>-10.11627906976744</v>
       </c>
       <c r="AP3">
-        <v>1.975945017182131</v>
+        <v>-0.867241379310345</v>
       </c>
       <c r="AQ3">
-        <v>-3.043062200956938</v>
+        <v>-10.11627906976744</v>
       </c>
     </row>
   </sheetData>
